--- a/AAII_Financials/Yearly/CWD_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CWD_YR_FIN.xlsx
@@ -2308,7 +2308,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>18400</v>
+        <v>18800</v>
       </c>
       <c r="E58" s="3">
         <v>9800</v>
@@ -2380,7 +2380,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>28500</v>
+        <v>28900</v>
       </c>
       <c r="E60" s="3">
         <v>21000</v>
@@ -2416,7 +2416,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>74700</v>
+        <v>74300</v>
       </c>
       <c r="E61" s="3">
         <v>72000</v>
